--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,49 +473,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1674000</v>
+        <v>21000</v>
       </c>
       <c r="F2" t="n">
-        <v>75</v>
+        <v>1005</v>
       </c>
       <c r="G2" t="n">
-        <v>125550000</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>21105000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.48</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -524,62 +526,62 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>50900</v>
+        <v>131200</v>
       </c>
       <c r="F3" t="n">
-        <v>413</v>
+        <v>305</v>
       </c>
       <c r="G3" t="n">
-        <v>21021700</v>
+        <v>40016000</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>14970</v>
+        <v>21900</v>
       </c>
       <c r="F4" t="n">
-        <v>1403</v>
+        <v>639</v>
       </c>
       <c r="G4" t="n">
-        <v>21002910</v>
+        <v>13994100</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -588,47 +590,49 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>28100</v>
+        <v>135300</v>
       </c>
       <c r="F5" t="n">
-        <v>747</v>
+        <v>155</v>
       </c>
       <c r="G5" t="n">
-        <v>20990700</v>
+        <v>20971500</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>260000</v>
+        <v>171200</v>
       </c>
       <c r="F6" t="n">
-        <v>485</v>
+        <v>231</v>
       </c>
       <c r="G6" t="n">
-        <v>126100000</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>39547200</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-1.21</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -638,12 +642,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -652,13 +656,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>311500</v>
+        <v>1674000</v>
       </c>
       <c r="F7" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="G7" t="n">
-        <v>20870500</v>
+        <v>125550000</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -670,12 +674,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -684,13 +688,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>36300</v>
+        <v>50900</v>
       </c>
       <c r="F8" t="n">
-        <v>579</v>
+        <v>413</v>
       </c>
       <c r="G8" t="n">
-        <v>21017700</v>
+        <v>21021700</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -702,12 +706,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -716,13 +720,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>577000</v>
+        <v>14970</v>
       </c>
       <c r="F9" t="n">
-        <v>36</v>
+        <v>1403</v>
       </c>
       <c r="G9" t="n">
-        <v>20772000</v>
+        <v>21002910</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -734,12 +738,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -748,13 +752,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>20900</v>
+        <v>28100</v>
       </c>
       <c r="F10" t="n">
-        <v>1005</v>
+        <v>747</v>
       </c>
       <c r="G10" t="n">
-        <v>21004500</v>
+        <v>20990700</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -766,12 +770,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -780,13 +784,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>150100</v>
+        <v>260000</v>
       </c>
       <c r="F11" t="n">
-        <v>140</v>
+        <v>485</v>
       </c>
       <c r="G11" t="n">
-        <v>21014000</v>
+        <v>126100000</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -798,12 +802,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -812,13 +816,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>94200</v>
+        <v>311500</v>
       </c>
       <c r="F12" t="n">
-        <v>297</v>
+        <v>67</v>
       </c>
       <c r="G12" t="n">
-        <v>27977400</v>
+        <v>20870500</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -830,12 +834,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -844,13 +848,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>116400</v>
+        <v>36300</v>
       </c>
       <c r="F13" t="n">
-        <v>180</v>
+        <v>579</v>
       </c>
       <c r="G13" t="n">
-        <v>20952000</v>
+        <v>21017700</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -862,12 +866,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -876,13 +880,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>22250</v>
+        <v>577000</v>
       </c>
       <c r="F14" t="n">
-        <v>1348</v>
+        <v>36</v>
       </c>
       <c r="G14" t="n">
-        <v>29993000</v>
+        <v>20772000</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -894,12 +898,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -908,13 +912,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>173300</v>
+        <v>20900</v>
       </c>
       <c r="F15" t="n">
-        <v>231</v>
+        <v>1005</v>
       </c>
       <c r="G15" t="n">
-        <v>40032300</v>
+        <v>21004500</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -926,12 +930,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -940,13 +944,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>35900</v>
+        <v>150100</v>
       </c>
       <c r="F16" t="n">
-        <v>585</v>
+        <v>140</v>
       </c>
       <c r="G16" t="n">
-        <v>21001500</v>
+        <v>21014000</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -958,12 +962,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -972,13 +976,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>21500</v>
+        <v>94200</v>
       </c>
       <c r="F17" t="n">
-        <v>977</v>
+        <v>297</v>
       </c>
       <c r="G17" t="n">
-        <v>21005500</v>
+        <v>27977400</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -990,12 +994,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1004,13 +1008,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>307500</v>
+        <v>116400</v>
       </c>
       <c r="F18" t="n">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="G18" t="n">
-        <v>24907500</v>
+        <v>20952000</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1022,12 +1026,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1036,13 +1040,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>129300</v>
+        <v>22250</v>
       </c>
       <c r="F19" t="n">
-        <v>162</v>
+        <v>1348</v>
       </c>
       <c r="G19" t="n">
-        <v>20946600</v>
+        <v>29993000</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1054,12 +1058,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1068,13 +1072,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>54200</v>
+        <v>173300</v>
       </c>
       <c r="F20" t="n">
-        <v>387</v>
+        <v>231</v>
       </c>
       <c r="G20" t="n">
-        <v>20975400</v>
+        <v>40032300</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1086,12 +1090,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1100,13 +1104,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>139000</v>
+        <v>35900</v>
       </c>
       <c r="F21" t="n">
-        <v>151</v>
+        <v>585</v>
       </c>
       <c r="G21" t="n">
-        <v>20989000</v>
+        <v>21001500</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1118,12 +1122,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1132,13 +1136,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>33800</v>
+        <v>21500</v>
       </c>
       <c r="F22" t="n">
-        <v>621</v>
+        <v>977</v>
       </c>
       <c r="G22" t="n">
-        <v>20989800</v>
+        <v>21005500</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1150,12 +1154,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1164,13 +1168,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>142300</v>
+        <v>307500</v>
       </c>
       <c r="F23" t="n">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="G23" t="n">
-        <v>21060400</v>
+        <v>24907500</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1182,29 +1186,189 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>222800</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>129300</v>
+      </c>
+      <c r="F24" t="n">
+        <v>162</v>
+      </c>
+      <c r="G24" t="n">
+        <v>20946600</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>54200</v>
+      </c>
+      <c r="F25" t="n">
+        <v>387</v>
+      </c>
+      <c r="G25" t="n">
+        <v>20975400</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>세아제강</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>306200</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>139000</v>
+      </c>
+      <c r="F26" t="n">
+        <v>151</v>
+      </c>
+      <c r="G26" t="n">
+        <v>20989000</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>33800</v>
+      </c>
+      <c r="F27" t="n">
+        <v>621</v>
+      </c>
+      <c r="G27" t="n">
+        <v>20989800</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>HD현대에너지솔루션</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>322000</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>142300</v>
+      </c>
+      <c r="F28" t="n">
+        <v>148</v>
+      </c>
+      <c r="G28" t="n">
+        <v>21060400</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>RF머트리얼즈</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>327260</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
         <v>36750</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F29" t="n">
         <v>1088</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G29" t="n">
         <v>39984000</v>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -561,10 +561,10 @@
         <v>21900</v>
       </c>
       <c r="F4" t="n">
-        <v>639</v>
+        <v>229</v>
       </c>
       <c r="G4" t="n">
-        <v>13994100</v>
+        <v>5015100</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,17 +473,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -492,32 +492,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>21000</v>
+        <v>32250</v>
       </c>
       <c r="F2" t="n">
-        <v>1005</v>
+        <v>579</v>
       </c>
       <c r="G2" t="n">
-        <v>21105000</v>
+        <v>18672750</v>
       </c>
       <c r="H2" t="n">
-        <v>0.48</v>
+        <v>-11.16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -526,94 +526,96 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>131200</v>
+        <v>27400</v>
       </c>
       <c r="F3" t="n">
-        <v>305</v>
+        <v>1095</v>
       </c>
       <c r="G3" t="n">
-        <v>40016000</v>
+        <v>30003000</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>21900</v>
+        <v>105800</v>
       </c>
       <c r="F4" t="n">
-        <v>229</v>
+        <v>180</v>
       </c>
       <c r="G4" t="n">
-        <v>5015100</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>19044000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-9.109999999999999</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>135300</v>
+        <v>124700</v>
       </c>
       <c r="F5" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="G5" t="n">
-        <v>20971500</v>
+        <v>19952000</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -622,32 +624,32 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>171200</v>
+        <v>33750</v>
       </c>
       <c r="F6" t="n">
-        <v>231</v>
+        <v>585</v>
       </c>
       <c r="G6" t="n">
-        <v>39547200</v>
+        <v>19743750</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.21</v>
+        <v>-5.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -656,30 +658,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1674000</v>
+        <v>33750</v>
       </c>
       <c r="F7" t="n">
-        <v>75</v>
+        <v>889</v>
       </c>
       <c r="G7" t="n">
-        <v>125550000</v>
+        <v>30003750</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -688,62 +690,64 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>50900</v>
+        <v>86300</v>
       </c>
       <c r="F8" t="n">
-        <v>413</v>
+        <v>243</v>
       </c>
       <c r="G8" t="n">
-        <v>21021700</v>
+        <v>20970900</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>14970</v>
+        <v>21000</v>
       </c>
       <c r="F9" t="n">
-        <v>1403</v>
+        <v>1005</v>
       </c>
       <c r="G9" t="n">
-        <v>21002910</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
+        <v>21105000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.48</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -752,62 +756,62 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>28100</v>
+        <v>131200</v>
       </c>
       <c r="F10" t="n">
-        <v>747</v>
+        <v>305</v>
       </c>
       <c r="G10" t="n">
-        <v>20990700</v>
+        <v>40016000</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>260000</v>
+        <v>21900</v>
       </c>
       <c r="F11" t="n">
-        <v>485</v>
+        <v>229</v>
       </c>
       <c r="G11" t="n">
-        <v>126100000</v>
+        <v>5015100</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -816,47 +820,49 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>311500</v>
+        <v>135300</v>
       </c>
       <c r="F12" t="n">
-        <v>67</v>
+        <v>155</v>
       </c>
       <c r="G12" t="n">
-        <v>20870500</v>
+        <v>20971500</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>36300</v>
+        <v>171200</v>
       </c>
       <c r="F13" t="n">
-        <v>579</v>
+        <v>231</v>
       </c>
       <c r="G13" t="n">
-        <v>21017700</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>39547200</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-1.21</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -866,12 +872,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -880,13 +886,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>577000</v>
+        <v>1674000</v>
       </c>
       <c r="F14" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="G14" t="n">
-        <v>20772000</v>
+        <v>125550000</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -898,12 +904,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -912,13 +918,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>20900</v>
+        <v>50900</v>
       </c>
       <c r="F15" t="n">
-        <v>1005</v>
+        <v>413</v>
       </c>
       <c r="G15" t="n">
-        <v>21004500</v>
+        <v>21021700</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -930,12 +936,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -944,13 +950,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>150100</v>
+        <v>14970</v>
       </c>
       <c r="F16" t="n">
-        <v>140</v>
+        <v>1403</v>
       </c>
       <c r="G16" t="n">
-        <v>21014000</v>
+        <v>21002910</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -962,12 +968,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -976,13 +982,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>94200</v>
+        <v>28100</v>
       </c>
       <c r="F17" t="n">
-        <v>297</v>
+        <v>747</v>
       </c>
       <c r="G17" t="n">
-        <v>27977400</v>
+        <v>20990700</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -994,12 +1000,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1008,13 +1014,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>116400</v>
+        <v>260000</v>
       </c>
       <c r="F18" t="n">
-        <v>180</v>
+        <v>485</v>
       </c>
       <c r="G18" t="n">
-        <v>20952000</v>
+        <v>126100000</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1026,12 +1032,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1040,13 +1046,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>22250</v>
+        <v>311500</v>
       </c>
       <c r="F19" t="n">
-        <v>1348</v>
+        <v>67</v>
       </c>
       <c r="G19" t="n">
-        <v>29993000</v>
+        <v>20870500</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1058,12 +1064,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1072,13 +1078,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>173300</v>
+        <v>36300</v>
       </c>
       <c r="F20" t="n">
-        <v>231</v>
+        <v>579</v>
       </c>
       <c r="G20" t="n">
-        <v>40032300</v>
+        <v>21017700</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1090,12 +1096,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1104,13 +1110,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>35900</v>
+        <v>577000</v>
       </c>
       <c r="F21" t="n">
-        <v>585</v>
+        <v>36</v>
       </c>
       <c r="G21" t="n">
-        <v>21001500</v>
+        <v>20772000</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1122,12 +1128,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1136,13 +1142,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>21500</v>
+        <v>20900</v>
       </c>
       <c r="F22" t="n">
-        <v>977</v>
+        <v>1005</v>
       </c>
       <c r="G22" t="n">
-        <v>21005500</v>
+        <v>21004500</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1154,12 +1160,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1168,13 +1174,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>307500</v>
+        <v>150100</v>
       </c>
       <c r="F23" t="n">
-        <v>81</v>
+        <v>140</v>
       </c>
       <c r="G23" t="n">
-        <v>24907500</v>
+        <v>21014000</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1186,12 +1192,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1200,13 +1206,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>129300</v>
+        <v>94200</v>
       </c>
       <c r="F24" t="n">
-        <v>162</v>
+        <v>297</v>
       </c>
       <c r="G24" t="n">
-        <v>20946600</v>
+        <v>27977400</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1218,12 +1224,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1232,13 +1238,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>54200</v>
+        <v>116400</v>
       </c>
       <c r="F25" t="n">
-        <v>387</v>
+        <v>180</v>
       </c>
       <c r="G25" t="n">
-        <v>20975400</v>
+        <v>20952000</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1250,12 +1256,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1264,13 +1270,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>139000</v>
+        <v>22250</v>
       </c>
       <c r="F26" t="n">
-        <v>151</v>
+        <v>1348</v>
       </c>
       <c r="G26" t="n">
-        <v>20989000</v>
+        <v>29993000</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1282,12 +1288,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1296,13 +1302,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>33800</v>
+        <v>173300</v>
       </c>
       <c r="F27" t="n">
-        <v>621</v>
+        <v>231</v>
       </c>
       <c r="G27" t="n">
-        <v>20989800</v>
+        <v>40032300</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1314,12 +1320,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1328,13 +1334,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>142300</v>
+        <v>35900</v>
       </c>
       <c r="F28" t="n">
-        <v>148</v>
+        <v>585</v>
       </c>
       <c r="G28" t="n">
-        <v>21060400</v>
+        <v>21001500</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1346,29 +1352,253 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>아스플로</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>159010</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>21500</v>
+      </c>
+      <c r="F29" t="n">
+        <v>977</v>
+      </c>
+      <c r="G29" t="n">
+        <v>21005500</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>196170</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>307500</v>
+      </c>
+      <c r="F30" t="n">
+        <v>81</v>
+      </c>
+      <c r="G30" t="n">
+        <v>24907500</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>222800</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>129300</v>
+      </c>
+      <c r="F31" t="n">
+        <v>162</v>
+      </c>
+      <c r="G31" t="n">
+        <v>20946600</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>54200</v>
+      </c>
+      <c r="F32" t="n">
+        <v>387</v>
+      </c>
+      <c r="G32" t="n">
+        <v>20975400</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>세아제강</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>306200</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>139000</v>
+      </c>
+      <c r="F33" t="n">
+        <v>151</v>
+      </c>
+      <c r="G33" t="n">
+        <v>20989000</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>33800</v>
+      </c>
+      <c r="F34" t="n">
+        <v>621</v>
+      </c>
+      <c r="G34" t="n">
+        <v>20989800</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>HD현대에너지솔루션</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>322000</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>142300</v>
+      </c>
+      <c r="F35" t="n">
+        <v>148</v>
+      </c>
+      <c r="G35" t="n">
+        <v>21060400</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>RF머트리얼즈</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>327260</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
         <v>36750</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F36" t="n">
         <v>1088</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G36" t="n">
         <v>39984000</v>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -529,10 +529,10 @@
         <v>27400</v>
       </c>
       <c r="F3" t="n">
-        <v>1095</v>
+        <v>1086</v>
       </c>
       <c r="G3" t="n">
-        <v>30003000</v>
+        <v>29756400</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
@@ -595,10 +595,10 @@
         <v>124700</v>
       </c>
       <c r="F5" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G5" t="n">
-        <v>19952000</v>
+        <v>19827300</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -661,10 +661,10 @@
         <v>33750</v>
       </c>
       <c r="F7" t="n">
-        <v>889</v>
+        <v>882</v>
       </c>
       <c r="G7" t="n">
-        <v>30003750</v>
+        <v>29767500</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -693,10 +693,10 @@
         <v>86300</v>
       </c>
       <c r="F8" t="n">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G8" t="n">
-        <v>20970900</v>
+        <v>20798300</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,36 +473,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>32250</v>
+        <v>21800</v>
       </c>
       <c r="F2" t="n">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="G2" t="n">
-        <v>18672750</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-11.16</v>
-      </c>
+        <v>12665800</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,29 +510,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>27400</v>
+        <v>32250</v>
       </c>
       <c r="F3" t="n">
-        <v>1086</v>
+        <v>579</v>
       </c>
       <c r="G3" t="n">
-        <v>29756400</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>18672750</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-11.16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -544,31 +544,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105800</v>
+        <v>27400</v>
       </c>
       <c r="F4" t="n">
-        <v>180</v>
+        <v>1086</v>
       </c>
       <c r="G4" t="n">
-        <v>19044000</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-9.109999999999999</v>
-      </c>
+        <v>29756400</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -578,29 +576,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>124700</v>
+        <v>105800</v>
       </c>
       <c r="F5" t="n">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="G5" t="n">
-        <v>19827300</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>19044000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-9.109999999999999</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -610,31 +610,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>33750</v>
+        <v>124700</v>
       </c>
       <c r="F6" t="n">
-        <v>585</v>
+        <v>159</v>
       </c>
       <c r="G6" t="n">
-        <v>19743750</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-5.99</v>
-      </c>
+        <v>19827300</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -654,7 +652,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -676,63 +674,61 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>86300</v>
+        <v>33750</v>
       </c>
       <c r="F8" t="n">
-        <v>241</v>
+        <v>585</v>
       </c>
       <c r="G8" t="n">
-        <v>20798300</v>
+        <v>19743750</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>21000</v>
+        <v>86300</v>
       </c>
       <c r="F9" t="n">
-        <v>1005</v>
+        <v>241</v>
       </c>
       <c r="G9" t="n">
-        <v>21105000</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.48</v>
-      </c>
+        <v>20798300</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -742,29 +738,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>131200</v>
+        <v>21000</v>
       </c>
       <c r="F10" t="n">
-        <v>305</v>
+        <v>1005</v>
       </c>
       <c r="G10" t="n">
-        <v>40016000</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>21105000</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.48</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -774,27 +772,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>21900</v>
+        <v>131200</v>
       </c>
       <c r="F11" t="n">
-        <v>229</v>
+        <v>305</v>
       </c>
       <c r="G11" t="n">
-        <v>5015100</v>
+        <v>40016000</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -806,27 +804,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>135300</v>
+        <v>21900</v>
       </c>
       <c r="F12" t="n">
-        <v>155</v>
+        <v>229</v>
       </c>
       <c r="G12" t="n">
-        <v>20971500</v>
+        <v>5015100</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -838,63 +836,63 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>171200</v>
+        <v>135300</v>
       </c>
       <c r="F13" t="n">
-        <v>231</v>
+        <v>155</v>
       </c>
       <c r="G13" t="n">
-        <v>39547200</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-1.21</v>
-      </c>
+        <v>20971500</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1674000</v>
+        <v>171200</v>
       </c>
       <c r="F14" t="n">
-        <v>75</v>
+        <v>231</v>
       </c>
       <c r="G14" t="n">
-        <v>125550000</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
+        <v>39547200</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-1.21</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -904,12 +902,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -918,13 +916,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>50900</v>
+        <v>1674000</v>
       </c>
       <c r="F15" t="n">
-        <v>413</v>
+        <v>75</v>
       </c>
       <c r="G15" t="n">
-        <v>21021700</v>
+        <v>125550000</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -936,12 +934,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -950,13 +948,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>14970</v>
+        <v>50900</v>
       </c>
       <c r="F16" t="n">
-        <v>1403</v>
+        <v>413</v>
       </c>
       <c r="G16" t="n">
-        <v>21002910</v>
+        <v>21021700</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -968,12 +966,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -982,13 +980,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>28100</v>
+        <v>14970</v>
       </c>
       <c r="F17" t="n">
-        <v>747</v>
+        <v>1403</v>
       </c>
       <c r="G17" t="n">
-        <v>20990700</v>
+        <v>21002910</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -1000,12 +998,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1014,13 +1012,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>260000</v>
+        <v>28100</v>
       </c>
       <c r="F18" t="n">
-        <v>485</v>
+        <v>747</v>
       </c>
       <c r="G18" t="n">
-        <v>126100000</v>
+        <v>20990700</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1032,12 +1030,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1046,13 +1044,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>311500</v>
+        <v>260000</v>
       </c>
       <c r="F19" t="n">
-        <v>67</v>
+        <v>485</v>
       </c>
       <c r="G19" t="n">
-        <v>20870500</v>
+        <v>126100000</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1064,12 +1062,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1078,13 +1076,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>36300</v>
+        <v>311500</v>
       </c>
       <c r="F20" t="n">
-        <v>579</v>
+        <v>67</v>
       </c>
       <c r="G20" t="n">
-        <v>21017700</v>
+        <v>20870500</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1096,12 +1094,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1110,13 +1108,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>577000</v>
+        <v>36300</v>
       </c>
       <c r="F21" t="n">
-        <v>36</v>
+        <v>579</v>
       </c>
       <c r="G21" t="n">
-        <v>20772000</v>
+        <v>21017700</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1128,12 +1126,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1142,13 +1140,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>20900</v>
+        <v>577000</v>
       </c>
       <c r="F22" t="n">
-        <v>1005</v>
+        <v>36</v>
       </c>
       <c r="G22" t="n">
-        <v>21004500</v>
+        <v>20772000</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1160,12 +1158,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1174,13 +1172,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>150100</v>
+        <v>20900</v>
       </c>
       <c r="F23" t="n">
-        <v>140</v>
+        <v>1005</v>
       </c>
       <c r="G23" t="n">
-        <v>21014000</v>
+        <v>21004500</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1192,12 +1190,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1206,13 +1204,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>94200</v>
+        <v>150100</v>
       </c>
       <c r="F24" t="n">
-        <v>297</v>
+        <v>140</v>
       </c>
       <c r="G24" t="n">
-        <v>27977400</v>
+        <v>21014000</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1224,12 +1222,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1238,13 +1236,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>116400</v>
+        <v>94200</v>
       </c>
       <c r="F25" t="n">
-        <v>180</v>
+        <v>297</v>
       </c>
       <c r="G25" t="n">
-        <v>20952000</v>
+        <v>27977400</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1256,12 +1254,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1270,13 +1268,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>22250</v>
+        <v>116400</v>
       </c>
       <c r="F26" t="n">
-        <v>1348</v>
+        <v>180</v>
       </c>
       <c r="G26" t="n">
-        <v>29993000</v>
+        <v>20952000</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1288,12 +1286,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1302,13 +1300,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>173300</v>
+        <v>22250</v>
       </c>
       <c r="F27" t="n">
-        <v>231</v>
+        <v>1348</v>
       </c>
       <c r="G27" t="n">
-        <v>40032300</v>
+        <v>29993000</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1320,12 +1318,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1334,13 +1332,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>35900</v>
+        <v>173300</v>
       </c>
       <c r="F28" t="n">
-        <v>585</v>
+        <v>231</v>
       </c>
       <c r="G28" t="n">
-        <v>21001500</v>
+        <v>40032300</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1352,12 +1350,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1366,13 +1364,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>21500</v>
+        <v>35900</v>
       </c>
       <c r="F29" t="n">
-        <v>977</v>
+        <v>585</v>
       </c>
       <c r="G29" t="n">
-        <v>21005500</v>
+        <v>21001500</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1384,12 +1382,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1398,13 +1396,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>307500</v>
+        <v>21500</v>
       </c>
       <c r="F30" t="n">
-        <v>81</v>
+        <v>977</v>
       </c>
       <c r="G30" t="n">
-        <v>24907500</v>
+        <v>21005500</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1416,12 +1414,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1430,13 +1428,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>129300</v>
+        <v>307500</v>
       </c>
       <c r="F31" t="n">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="G31" t="n">
-        <v>20946600</v>
+        <v>24907500</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1448,12 +1446,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1462,13 +1460,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>54200</v>
+        <v>129300</v>
       </c>
       <c r="F32" t="n">
-        <v>387</v>
+        <v>162</v>
       </c>
       <c r="G32" t="n">
-        <v>20975400</v>
+        <v>20946600</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1480,12 +1478,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1494,13 +1492,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>139000</v>
+        <v>54200</v>
       </c>
       <c r="F33" t="n">
-        <v>151</v>
+        <v>387</v>
       </c>
       <c r="G33" t="n">
-        <v>20989000</v>
+        <v>20975400</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1512,12 +1510,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1526,13 +1524,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>33800</v>
+        <v>139000</v>
       </c>
       <c r="F34" t="n">
-        <v>621</v>
+        <v>151</v>
       </c>
       <c r="G34" t="n">
-        <v>20989800</v>
+        <v>20989000</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1544,12 +1542,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1558,13 +1556,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>142300</v>
+        <v>33800</v>
       </c>
       <c r="F35" t="n">
-        <v>148</v>
+        <v>621</v>
       </c>
       <c r="G35" t="n">
-        <v>21060400</v>
+        <v>20989800</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1576,29 +1574,61 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>HD현대에너지솔루션</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>322000</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>142300</v>
+      </c>
+      <c r="F36" t="n">
+        <v>148</v>
+      </c>
+      <c r="G36" t="n">
+        <v>21060400</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>RF머트리얼즈</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>327260</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
         <v>36750</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F37" t="n">
         <v>1088</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G37" t="n">
         <v>39984000</v>
       </c>
-      <c r="H36" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,134 +473,130 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>21800</v>
+        <v>92500</v>
       </c>
       <c r="F2" t="n">
-        <v>581</v>
+        <v>78</v>
       </c>
       <c r="G2" t="n">
-        <v>12665800</v>
+        <v>7215000</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>32250</v>
+        <v>25550</v>
       </c>
       <c r="F3" t="n">
-        <v>579</v>
+        <v>377</v>
       </c>
       <c r="G3" t="n">
-        <v>18672750</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-11.16</v>
-      </c>
+        <v>9632350</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>27400</v>
+        <v>25400</v>
       </c>
       <c r="F4" t="n">
-        <v>1086</v>
+        <v>379</v>
       </c>
       <c r="G4" t="n">
-        <v>29756400</v>
+        <v>9626600</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105800</v>
+        <v>21800</v>
       </c>
       <c r="F5" t="n">
-        <v>180</v>
+        <v>581</v>
       </c>
       <c r="G5" t="n">
-        <v>19044000</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-9.109999999999999</v>
-      </c>
+        <v>12665800</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -610,29 +606,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>124700</v>
+        <v>32250</v>
       </c>
       <c r="F6" t="n">
-        <v>159</v>
+        <v>579</v>
       </c>
       <c r="G6" t="n">
-        <v>19827300</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>18672750</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-11.16</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -642,27 +640,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>33750</v>
+        <v>27400</v>
       </c>
       <c r="F7" t="n">
-        <v>882</v>
+        <v>1086</v>
       </c>
       <c r="G7" t="n">
-        <v>29767500</v>
+        <v>29756400</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -674,29 +672,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>33750</v>
+        <v>105800</v>
       </c>
       <c r="F8" t="n">
-        <v>585</v>
+        <v>180</v>
       </c>
       <c r="G8" t="n">
-        <v>19743750</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+        <v>19044000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-9.109999999999999</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -706,44 +706,44 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>86300</v>
+        <v>124700</v>
       </c>
       <c r="F9" t="n">
-        <v>241</v>
+        <v>159</v>
       </c>
       <c r="G9" t="n">
-        <v>20798300</v>
+        <v>19827300</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -752,32 +752,32 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>21000</v>
+        <v>33750</v>
       </c>
       <c r="F10" t="n">
-        <v>1005</v>
+        <v>585</v>
       </c>
       <c r="G10" t="n">
-        <v>21105000</v>
+        <v>19743750</v>
       </c>
       <c r="H10" t="n">
-        <v>0.48</v>
+        <v>-5.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -786,45 +786,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>131200</v>
+        <v>33750</v>
       </c>
       <c r="F11" t="n">
-        <v>305</v>
+        <v>882</v>
       </c>
       <c r="G11" t="n">
-        <v>40016000</v>
+        <v>29767500</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>21900</v>
+        <v>86300</v>
       </c>
       <c r="F12" t="n">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="G12" t="n">
-        <v>5015100</v>
+        <v>20798300</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -836,29 +836,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>135300</v>
+        <v>21000</v>
       </c>
       <c r="F13" t="n">
-        <v>155</v>
+        <v>1005</v>
       </c>
       <c r="G13" t="n">
-        <v>20971500</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>21105000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.48</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -868,78 +870,76 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>171200</v>
+        <v>131200</v>
       </c>
       <c r="F14" t="n">
-        <v>231</v>
+        <v>305</v>
       </c>
       <c r="G14" t="n">
-        <v>39547200</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-1.21</v>
-      </c>
+        <v>40016000</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1674000</v>
+        <v>21900</v>
       </c>
       <c r="F15" t="n">
-        <v>75</v>
+        <v>229</v>
       </c>
       <c r="G15" t="n">
-        <v>125550000</v>
+        <v>5015100</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -948,47 +948,49 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>50900</v>
+        <v>135300</v>
       </c>
       <c r="F16" t="n">
-        <v>413</v>
+        <v>155</v>
       </c>
       <c r="G16" t="n">
-        <v>21021700</v>
+        <v>20971500</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>14970</v>
+        <v>171200</v>
       </c>
       <c r="F17" t="n">
-        <v>1403</v>
+        <v>231</v>
       </c>
       <c r="G17" t="n">
-        <v>21002910</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
+        <v>39547200</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-1.21</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -998,12 +1000,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1012,13 +1014,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>28100</v>
+        <v>1674000</v>
       </c>
       <c r="F18" t="n">
-        <v>747</v>
+        <v>75</v>
       </c>
       <c r="G18" t="n">
-        <v>20990700</v>
+        <v>125550000</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1030,12 +1032,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1044,13 +1046,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>260000</v>
+        <v>50900</v>
       </c>
       <c r="F19" t="n">
-        <v>485</v>
+        <v>413</v>
       </c>
       <c r="G19" t="n">
-        <v>126100000</v>
+        <v>21021700</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1062,12 +1064,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1076,13 +1078,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>311500</v>
+        <v>14970</v>
       </c>
       <c r="F20" t="n">
-        <v>67</v>
+        <v>1403</v>
       </c>
       <c r="G20" t="n">
-        <v>20870500</v>
+        <v>21002910</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1094,12 +1096,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1108,13 +1110,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>36300</v>
+        <v>28100</v>
       </c>
       <c r="F21" t="n">
-        <v>579</v>
+        <v>747</v>
       </c>
       <c r="G21" t="n">
-        <v>21017700</v>
+        <v>20990700</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1126,12 +1128,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1140,13 +1142,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>577000</v>
+        <v>260000</v>
       </c>
       <c r="F22" t="n">
-        <v>36</v>
+        <v>485</v>
       </c>
       <c r="G22" t="n">
-        <v>20772000</v>
+        <v>126100000</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1158,12 +1160,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1172,13 +1174,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>20900</v>
+        <v>311500</v>
       </c>
       <c r="F23" t="n">
-        <v>1005</v>
+        <v>67</v>
       </c>
       <c r="G23" t="n">
-        <v>21004500</v>
+        <v>20870500</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1190,12 +1192,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1204,13 +1206,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>150100</v>
+        <v>36300</v>
       </c>
       <c r="F24" t="n">
-        <v>140</v>
+        <v>579</v>
       </c>
       <c r="G24" t="n">
-        <v>21014000</v>
+        <v>21017700</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1222,12 +1224,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1236,13 +1238,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>94200</v>
+        <v>577000</v>
       </c>
       <c r="F25" t="n">
-        <v>297</v>
+        <v>36</v>
       </c>
       <c r="G25" t="n">
-        <v>27977400</v>
+        <v>20772000</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1254,12 +1256,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1268,13 +1270,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>116400</v>
+        <v>20900</v>
       </c>
       <c r="F26" t="n">
-        <v>180</v>
+        <v>1005</v>
       </c>
       <c r="G26" t="n">
-        <v>20952000</v>
+        <v>21004500</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1286,12 +1288,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1300,13 +1302,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>22250</v>
+        <v>150100</v>
       </c>
       <c r="F27" t="n">
-        <v>1348</v>
+        <v>140</v>
       </c>
       <c r="G27" t="n">
-        <v>29993000</v>
+        <v>21014000</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1318,12 +1320,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1332,13 +1334,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>173300</v>
+        <v>94200</v>
       </c>
       <c r="F28" t="n">
-        <v>231</v>
+        <v>297</v>
       </c>
       <c r="G28" t="n">
-        <v>40032300</v>
+        <v>27977400</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1350,12 +1352,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1364,13 +1366,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>35900</v>
+        <v>116400</v>
       </c>
       <c r="F29" t="n">
-        <v>585</v>
+        <v>180</v>
       </c>
       <c r="G29" t="n">
-        <v>21001500</v>
+        <v>20952000</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1382,12 +1384,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1396,13 +1398,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>21500</v>
+        <v>22250</v>
       </c>
       <c r="F30" t="n">
-        <v>977</v>
+        <v>1348</v>
       </c>
       <c r="G30" t="n">
-        <v>21005500</v>
+        <v>29993000</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1414,12 +1416,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1428,13 +1430,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>307500</v>
+        <v>173300</v>
       </c>
       <c r="F31" t="n">
-        <v>81</v>
+        <v>231</v>
       </c>
       <c r="G31" t="n">
-        <v>24907500</v>
+        <v>40032300</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1446,12 +1448,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1460,13 +1462,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>129300</v>
+        <v>35900</v>
       </c>
       <c r="F32" t="n">
-        <v>162</v>
+        <v>585</v>
       </c>
       <c r="G32" t="n">
-        <v>20946600</v>
+        <v>21001500</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1478,12 +1480,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1492,13 +1494,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>54200</v>
+        <v>21500</v>
       </c>
       <c r="F33" t="n">
-        <v>387</v>
+        <v>977</v>
       </c>
       <c r="G33" t="n">
-        <v>20975400</v>
+        <v>21005500</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1510,12 +1512,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1524,13 +1526,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>139000</v>
+        <v>307500</v>
       </c>
       <c r="F34" t="n">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="G34" t="n">
-        <v>20989000</v>
+        <v>24907500</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1542,12 +1544,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1556,13 +1558,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>33800</v>
+        <v>129300</v>
       </c>
       <c r="F35" t="n">
-        <v>621</v>
+        <v>162</v>
       </c>
       <c r="G35" t="n">
-        <v>20989800</v>
+        <v>20946600</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1574,12 +1576,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1588,13 +1590,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>142300</v>
+        <v>54200</v>
       </c>
       <c r="F36" t="n">
-        <v>148</v>
+        <v>387</v>
       </c>
       <c r="G36" t="n">
-        <v>21060400</v>
+        <v>20975400</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1606,29 +1608,125 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>세아제강</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>306200</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>139000</v>
+      </c>
+      <c r="F37" t="n">
+        <v>151</v>
+      </c>
+      <c r="G37" t="n">
+        <v>20989000</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>33800</v>
+      </c>
+      <c r="F38" t="n">
+        <v>621</v>
+      </c>
+      <c r="G38" t="n">
+        <v>20989800</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>HD현대에너지솔루션</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>322000</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>142300</v>
+      </c>
+      <c r="F39" t="n">
+        <v>148</v>
+      </c>
+      <c r="G39" t="n">
+        <v>21060400</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>RF머트리얼즈</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>327260</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
         <v>36750</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F40" t="n">
         <v>1088</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G40" t="n">
         <v>39984000</v>
       </c>
-      <c r="H37" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,17 +473,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -492,30 +492,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>92500</v>
+        <v>114500</v>
       </c>
       <c r="F2" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G2" t="n">
-        <v>7215000</v>
+        <v>9732500</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -524,179 +524,175 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>25550</v>
+        <v>24100</v>
       </c>
       <c r="F3" t="n">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="G3" t="n">
-        <v>9632350</v>
+        <v>9784600</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>25400</v>
+        <v>33750</v>
       </c>
       <c r="F4" t="n">
-        <v>379</v>
+        <v>290</v>
       </c>
       <c r="G4" t="n">
-        <v>9626600</v>
+        <v>9787500</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>21800</v>
+        <v>92500</v>
       </c>
       <c r="F5" t="n">
-        <v>581</v>
+        <v>78</v>
       </c>
       <c r="G5" t="n">
-        <v>12665800</v>
+        <v>7215000</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>32250</v>
+        <v>25550</v>
       </c>
       <c r="F6" t="n">
-        <v>579</v>
+        <v>377</v>
       </c>
       <c r="G6" t="n">
-        <v>18672750</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-11.16</v>
-      </c>
+        <v>9632350</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>27400</v>
+        <v>25400</v>
       </c>
       <c r="F7" t="n">
-        <v>1086</v>
+        <v>379</v>
       </c>
       <c r="G7" t="n">
-        <v>29756400</v>
+        <v>9626600</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105800</v>
+        <v>21800</v>
       </c>
       <c r="F8" t="n">
-        <v>180</v>
+        <v>581</v>
       </c>
       <c r="G8" t="n">
-        <v>19044000</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-9.109999999999999</v>
-      </c>
+        <v>12665800</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -706,29 +702,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>124700</v>
+        <v>32250</v>
       </c>
       <c r="F9" t="n">
-        <v>159</v>
+        <v>579</v>
       </c>
       <c r="G9" t="n">
-        <v>19827300</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
+        <v>18672750</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-11.16</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -738,31 +736,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>33750</v>
+        <v>27400</v>
       </c>
       <c r="F10" t="n">
-        <v>585</v>
+        <v>1086</v>
       </c>
       <c r="G10" t="n">
-        <v>19743750</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-5.99</v>
-      </c>
+        <v>29756400</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -772,29 +768,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>33750</v>
+        <v>105800</v>
       </c>
       <c r="F11" t="n">
-        <v>882</v>
+        <v>180</v>
       </c>
       <c r="G11" t="n">
-        <v>29767500</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
+        <v>19044000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-9.109999999999999</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -804,44 +802,44 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>86300</v>
+        <v>124700</v>
       </c>
       <c r="F12" t="n">
-        <v>241</v>
+        <v>159</v>
       </c>
       <c r="G12" t="n">
-        <v>20798300</v>
+        <v>19827300</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -850,32 +848,32 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>21000</v>
+        <v>33750</v>
       </c>
       <c r="F13" t="n">
-        <v>1005</v>
+        <v>585</v>
       </c>
       <c r="G13" t="n">
-        <v>21105000</v>
+        <v>19743750</v>
       </c>
       <c r="H13" t="n">
-        <v>0.48</v>
+        <v>-5.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -884,45 +882,45 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>131200</v>
+        <v>33750</v>
       </c>
       <c r="F14" t="n">
-        <v>305</v>
+        <v>882</v>
       </c>
       <c r="G14" t="n">
-        <v>40016000</v>
+        <v>29767500</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>21900</v>
+        <v>86300</v>
       </c>
       <c r="F15" t="n">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="G15" t="n">
-        <v>5015100</v>
+        <v>20798300</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -934,29 +932,31 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>135300</v>
+        <v>21000</v>
       </c>
       <c r="F16" t="n">
-        <v>155</v>
+        <v>1005</v>
       </c>
       <c r="G16" t="n">
-        <v>20971500</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
+        <v>21105000</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.48</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -966,78 +966,76 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>171200</v>
+        <v>131200</v>
       </c>
       <c r="F17" t="n">
-        <v>231</v>
+        <v>305</v>
       </c>
       <c r="G17" t="n">
-        <v>39547200</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-1.21</v>
-      </c>
+        <v>40016000</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1674000</v>
+        <v>21900</v>
       </c>
       <c r="F18" t="n">
-        <v>75</v>
+        <v>229</v>
       </c>
       <c r="G18" t="n">
-        <v>125550000</v>
+        <v>5015100</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1046,47 +1044,49 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>50900</v>
+        <v>135300</v>
       </c>
       <c r="F19" t="n">
-        <v>413</v>
+        <v>155</v>
       </c>
       <c r="G19" t="n">
-        <v>21021700</v>
+        <v>20971500</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>14970</v>
+        <v>171200</v>
       </c>
       <c r="F20" t="n">
-        <v>1403</v>
+        <v>231</v>
       </c>
       <c r="G20" t="n">
-        <v>21002910</v>
-      </c>
-      <c r="H20" t="inlineStr"/>
+        <v>39547200</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-1.21</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1110,13 +1110,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>28100</v>
+        <v>1674000</v>
       </c>
       <c r="F21" t="n">
-        <v>747</v>
+        <v>75</v>
       </c>
       <c r="G21" t="n">
-        <v>20990700</v>
+        <v>125550000</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1142,13 +1142,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>260000</v>
+        <v>50900</v>
       </c>
       <c r="F22" t="n">
-        <v>485</v>
+        <v>413</v>
       </c>
       <c r="G22" t="n">
-        <v>126100000</v>
+        <v>21021700</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1174,13 +1174,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>311500</v>
+        <v>14970</v>
       </c>
       <c r="F23" t="n">
-        <v>67</v>
+        <v>1403</v>
       </c>
       <c r="G23" t="n">
-        <v>20870500</v>
+        <v>21002910</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>36300</v>
+        <v>28100</v>
       </c>
       <c r="F24" t="n">
-        <v>579</v>
+        <v>747</v>
       </c>
       <c r="G24" t="n">
-        <v>21017700</v>
+        <v>20990700</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1238,13 +1238,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>577000</v>
+        <v>260000</v>
       </c>
       <c r="F25" t="n">
-        <v>36</v>
+        <v>485</v>
       </c>
       <c r="G25" t="n">
-        <v>20772000</v>
+        <v>126100000</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1270,13 +1270,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>20900</v>
+        <v>311500</v>
       </c>
       <c r="F26" t="n">
-        <v>1005</v>
+        <v>67</v>
       </c>
       <c r="G26" t="n">
-        <v>21004500</v>
+        <v>20870500</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1302,13 +1302,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>150100</v>
+        <v>36300</v>
       </c>
       <c r="F27" t="n">
-        <v>140</v>
+        <v>579</v>
       </c>
       <c r="G27" t="n">
-        <v>21014000</v>
+        <v>21017700</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>94200</v>
+        <v>577000</v>
       </c>
       <c r="F28" t="n">
-        <v>297</v>
+        <v>36</v>
       </c>
       <c r="G28" t="n">
-        <v>27977400</v>
+        <v>20772000</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1366,13 +1366,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>116400</v>
+        <v>20900</v>
       </c>
       <c r="F29" t="n">
-        <v>180</v>
+        <v>1005</v>
       </c>
       <c r="G29" t="n">
-        <v>20952000</v>
+        <v>21004500</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1398,13 +1398,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>22250</v>
+        <v>150100</v>
       </c>
       <c r="F30" t="n">
-        <v>1348</v>
+        <v>140</v>
       </c>
       <c r="G30" t="n">
-        <v>29993000</v>
+        <v>21014000</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1430,13 +1430,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>173300</v>
+        <v>94200</v>
       </c>
       <c r="F31" t="n">
-        <v>231</v>
+        <v>297</v>
       </c>
       <c r="G31" t="n">
-        <v>40032300</v>
+        <v>27977400</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1462,13 +1462,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>35900</v>
+        <v>116400</v>
       </c>
       <c r="F32" t="n">
-        <v>585</v>
+        <v>180</v>
       </c>
       <c r="G32" t="n">
-        <v>21001500</v>
+        <v>20952000</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1480,12 +1480,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1494,13 +1494,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>21500</v>
+        <v>22250</v>
       </c>
       <c r="F33" t="n">
-        <v>977</v>
+        <v>1348</v>
       </c>
       <c r="G33" t="n">
-        <v>21005500</v>
+        <v>29993000</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>307500</v>
+        <v>173300</v>
       </c>
       <c r="F34" t="n">
-        <v>81</v>
+        <v>231</v>
       </c>
       <c r="G34" t="n">
-        <v>24907500</v>
+        <v>40032300</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1544,12 +1544,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1558,13 +1558,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>129300</v>
+        <v>35900</v>
       </c>
       <c r="F35" t="n">
-        <v>162</v>
+        <v>585</v>
       </c>
       <c r="G35" t="n">
-        <v>20946600</v>
+        <v>21001500</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1576,12 +1576,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1590,13 +1590,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>54200</v>
+        <v>21500</v>
       </c>
       <c r="F36" t="n">
-        <v>387</v>
+        <v>977</v>
       </c>
       <c r="G36" t="n">
-        <v>20975400</v>
+        <v>21005500</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1608,12 +1608,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1622,13 +1622,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>139000</v>
+        <v>307500</v>
       </c>
       <c r="F37" t="n">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="G37" t="n">
-        <v>20989000</v>
+        <v>24907500</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1654,13 +1654,13 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>33800</v>
+        <v>129300</v>
       </c>
       <c r="F38" t="n">
-        <v>621</v>
+        <v>162</v>
       </c>
       <c r="G38" t="n">
-        <v>20989800</v>
+        <v>20946600</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1686,13 +1686,13 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>142300</v>
+        <v>54200</v>
       </c>
       <c r="F39" t="n">
-        <v>148</v>
+        <v>387</v>
       </c>
       <c r="G39" t="n">
-        <v>21060400</v>
+        <v>20975400</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1704,29 +1704,125 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>세아제강</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>306200</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>139000</v>
+      </c>
+      <c r="F40" t="n">
+        <v>151</v>
+      </c>
+      <c r="G40" t="n">
+        <v>20989000</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>33800</v>
+      </c>
+      <c r="F41" t="n">
+        <v>621</v>
+      </c>
+      <c r="G41" t="n">
+        <v>20989800</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>HD현대에너지솔루션</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>322000</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>142300</v>
+      </c>
+      <c r="F42" t="n">
+        <v>148</v>
+      </c>
+      <c r="G42" t="n">
+        <v>21060400</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>RF머트리얼즈</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>327260</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
         <v>36750</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F43" t="n">
         <v>1088</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G43" t="n">
         <v>39984000</v>
       </c>
-      <c r="H40" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -492,45 +492,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>114500</v>
+        <v>113700</v>
       </c>
       <c r="F2" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G2" t="n">
-        <v>9732500</v>
+        <v>9891900</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>24100</v>
+        <v>78600</v>
       </c>
       <c r="F3" t="n">
-        <v>406</v>
+        <v>264</v>
       </c>
       <c r="G3" t="n">
-        <v>9784600</v>
+        <v>20750400</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
@@ -542,12 +542,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -556,77 +556,77 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>33750</v>
+        <v>114500</v>
       </c>
       <c r="F4" t="n">
-        <v>290</v>
+        <v>85</v>
       </c>
       <c r="G4" t="n">
-        <v>9787500</v>
+        <v>9732500</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>92500</v>
+        <v>24100</v>
       </c>
       <c r="F5" t="n">
-        <v>78</v>
+        <v>406</v>
       </c>
       <c r="G5" t="n">
-        <v>7215000</v>
+        <v>9784600</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>25550</v>
+        <v>33750</v>
       </c>
       <c r="F6" t="n">
-        <v>377</v>
+        <v>290</v>
       </c>
       <c r="G6" t="n">
-        <v>9632350</v>
+        <v>9787500</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -638,44 +638,44 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>25400</v>
+        <v>92500</v>
       </c>
       <c r="F7" t="n">
-        <v>379</v>
+        <v>78</v>
       </c>
       <c r="G7" t="n">
-        <v>9626600</v>
+        <v>7215000</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -684,79 +684,77 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>21800</v>
+        <v>25550</v>
       </c>
       <c r="F8" t="n">
-        <v>581</v>
+        <v>377</v>
       </c>
       <c r="G8" t="n">
-        <v>12665800</v>
+        <v>9632350</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>32250</v>
+        <v>25400</v>
       </c>
       <c r="F9" t="n">
-        <v>579</v>
+        <v>379</v>
       </c>
       <c r="G9" t="n">
-        <v>18672750</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-11.16</v>
-      </c>
+        <v>9626600</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>27400</v>
+        <v>21800</v>
       </c>
       <c r="F10" t="n">
-        <v>1086</v>
+        <v>581</v>
       </c>
       <c r="G10" t="n">
-        <v>29756400</v>
+        <v>12665800</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -768,12 +766,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -782,16 +780,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105800</v>
+        <v>32250</v>
       </c>
       <c r="F11" t="n">
-        <v>180</v>
+        <v>579</v>
       </c>
       <c r="G11" t="n">
-        <v>19044000</v>
+        <v>18672750</v>
       </c>
       <c r="H11" t="n">
-        <v>-9.109999999999999</v>
+        <v>-11.16</v>
       </c>
     </row>
     <row r="12">
@@ -802,27 +800,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>124700</v>
+        <v>27400</v>
       </c>
       <c r="F12" t="n">
-        <v>159</v>
+        <v>1086</v>
       </c>
       <c r="G12" t="n">
-        <v>19827300</v>
+        <v>29756400</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -834,12 +832,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -848,16 +846,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>33750</v>
+        <v>105800</v>
       </c>
       <c r="F13" t="n">
-        <v>585</v>
+        <v>180</v>
       </c>
       <c r="G13" t="n">
-        <v>19743750</v>
+        <v>19044000</v>
       </c>
       <c r="H13" t="n">
-        <v>-5.99</v>
+        <v>-9.109999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -868,27 +866,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>33750</v>
+        <v>124700</v>
       </c>
       <c r="F14" t="n">
-        <v>882</v>
+        <v>159</v>
       </c>
       <c r="G14" t="n">
-        <v>29767500</v>
+        <v>19827300</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -900,78 +898,76 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>86300</v>
+        <v>33750</v>
       </c>
       <c r="F15" t="n">
-        <v>241</v>
+        <v>882</v>
       </c>
       <c r="G15" t="n">
-        <v>20798300</v>
+        <v>29767500</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>21000</v>
+        <v>33750</v>
       </c>
       <c r="F16" t="n">
-        <v>1005</v>
+        <v>585</v>
       </c>
       <c r="G16" t="n">
-        <v>21105000</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.48</v>
-      </c>
+        <v>19743750</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -980,13 +976,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>131200</v>
+        <v>86300</v>
       </c>
       <c r="F17" t="n">
-        <v>305</v>
+        <v>241</v>
       </c>
       <c r="G17" t="n">
-        <v>40016000</v>
+        <v>20798300</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -998,29 +994,31 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>21900</v>
+        <v>21000</v>
       </c>
       <c r="F18" t="n">
-        <v>229</v>
+        <v>1005</v>
       </c>
       <c r="G18" t="n">
-        <v>5015100</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
+        <v>21105000</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.48</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1030,12 +1028,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1044,13 +1042,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>135300</v>
+        <v>131200</v>
       </c>
       <c r="F19" t="n">
-        <v>155</v>
+        <v>305</v>
       </c>
       <c r="G19" t="n">
-        <v>20971500</v>
+        <v>40016000</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1062,46 +1060,44 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>171200</v>
+        <v>21900</v>
       </c>
       <c r="F20" t="n">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G20" t="n">
-        <v>39547200</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-1.21</v>
-      </c>
+        <v>5015100</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1110,47 +1106,49 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1674000</v>
+        <v>135300</v>
       </c>
       <c r="F21" t="n">
-        <v>75</v>
+        <v>155</v>
       </c>
       <c r="G21" t="n">
-        <v>125550000</v>
+        <v>20971500</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>50900</v>
+        <v>171200</v>
       </c>
       <c r="F22" t="n">
-        <v>413</v>
+        <v>231</v>
       </c>
       <c r="G22" t="n">
-        <v>21021700</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>39547200</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-1.21</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1160,12 +1158,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1174,13 +1172,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>14970</v>
+        <v>1674000</v>
       </c>
       <c r="F23" t="n">
-        <v>1403</v>
+        <v>75</v>
       </c>
       <c r="G23" t="n">
-        <v>21002910</v>
+        <v>125550000</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1192,12 +1190,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1206,13 +1204,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>28100</v>
+        <v>50900</v>
       </c>
       <c r="F24" t="n">
-        <v>747</v>
+        <v>413</v>
       </c>
       <c r="G24" t="n">
-        <v>20990700</v>
+        <v>21021700</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1224,12 +1222,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1238,13 +1236,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>260000</v>
+        <v>14970</v>
       </c>
       <c r="F25" t="n">
-        <v>485</v>
+        <v>1403</v>
       </c>
       <c r="G25" t="n">
-        <v>126100000</v>
+        <v>21002910</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1256,12 +1254,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1270,13 +1268,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>311500</v>
+        <v>28100</v>
       </c>
       <c r="F26" t="n">
-        <v>67</v>
+        <v>747</v>
       </c>
       <c r="G26" t="n">
-        <v>20870500</v>
+        <v>20990700</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1288,12 +1286,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1302,13 +1300,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>36300</v>
+        <v>260000</v>
       </c>
       <c r="F27" t="n">
-        <v>579</v>
+        <v>485</v>
       </c>
       <c r="G27" t="n">
-        <v>21017700</v>
+        <v>126100000</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1320,12 +1318,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1334,13 +1332,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>577000</v>
+        <v>311500</v>
       </c>
       <c r="F28" t="n">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="G28" t="n">
-        <v>20772000</v>
+        <v>20870500</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1352,12 +1350,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1366,13 +1364,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>20900</v>
+        <v>36300</v>
       </c>
       <c r="F29" t="n">
-        <v>1005</v>
+        <v>579</v>
       </c>
       <c r="G29" t="n">
-        <v>21004500</v>
+        <v>21017700</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1384,12 +1382,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1398,13 +1396,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>150100</v>
+        <v>577000</v>
       </c>
       <c r="F30" t="n">
-        <v>140</v>
+        <v>36</v>
       </c>
       <c r="G30" t="n">
-        <v>21014000</v>
+        <v>20772000</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1416,12 +1414,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1430,13 +1428,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>94200</v>
+        <v>20900</v>
       </c>
       <c r="F31" t="n">
-        <v>297</v>
+        <v>1005</v>
       </c>
       <c r="G31" t="n">
-        <v>27977400</v>
+        <v>21004500</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1448,12 +1446,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1462,13 +1460,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>116400</v>
+        <v>150100</v>
       </c>
       <c r="F32" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="G32" t="n">
-        <v>20952000</v>
+        <v>21014000</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1480,12 +1478,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1494,13 +1492,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>22250</v>
+        <v>94200</v>
       </c>
       <c r="F33" t="n">
-        <v>1348</v>
+        <v>297</v>
       </c>
       <c r="G33" t="n">
-        <v>29993000</v>
+        <v>27977400</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1512,12 +1510,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1526,13 +1524,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>173300</v>
+        <v>116400</v>
       </c>
       <c r="F34" t="n">
-        <v>231</v>
+        <v>180</v>
       </c>
       <c r="G34" t="n">
-        <v>40032300</v>
+        <v>20952000</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1544,12 +1542,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1558,13 +1556,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>35900</v>
+        <v>22250</v>
       </c>
       <c r="F35" t="n">
-        <v>585</v>
+        <v>1348</v>
       </c>
       <c r="G35" t="n">
-        <v>21001500</v>
+        <v>29993000</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1576,12 +1574,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1590,13 +1588,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>21500</v>
+        <v>173300</v>
       </c>
       <c r="F36" t="n">
-        <v>977</v>
+        <v>231</v>
       </c>
       <c r="G36" t="n">
-        <v>21005500</v>
+        <v>40032300</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1608,12 +1606,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1622,13 +1620,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>307500</v>
+        <v>35900</v>
       </c>
       <c r="F37" t="n">
-        <v>81</v>
+        <v>585</v>
       </c>
       <c r="G37" t="n">
-        <v>24907500</v>
+        <v>21001500</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1640,12 +1638,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1654,13 +1652,13 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>129300</v>
+        <v>21500</v>
       </c>
       <c r="F38" t="n">
-        <v>162</v>
+        <v>977</v>
       </c>
       <c r="G38" t="n">
-        <v>20946600</v>
+        <v>21005500</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1672,12 +1670,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1686,13 +1684,13 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>54200</v>
+        <v>307500</v>
       </c>
       <c r="F39" t="n">
-        <v>387</v>
+        <v>81</v>
       </c>
       <c r="G39" t="n">
-        <v>20975400</v>
+        <v>24907500</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1704,12 +1702,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1718,13 +1716,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>139000</v>
+        <v>129300</v>
       </c>
       <c r="F40" t="n">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="G40" t="n">
-        <v>20989000</v>
+        <v>20946600</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1736,12 +1734,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1750,13 +1748,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>33800</v>
+        <v>54200</v>
       </c>
       <c r="F41" t="n">
-        <v>621</v>
+        <v>387</v>
       </c>
       <c r="G41" t="n">
-        <v>20989800</v>
+        <v>20975400</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1768,12 +1766,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1782,13 +1780,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>142300</v>
+        <v>139000</v>
       </c>
       <c r="F42" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G42" t="n">
-        <v>21060400</v>
+        <v>20989000</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1800,29 +1798,93 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>33800</v>
+      </c>
+      <c r="F43" t="n">
+        <v>621</v>
+      </c>
+      <c r="G43" t="n">
+        <v>20989800</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>HD현대에너지솔루션</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>322000</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>142300</v>
+      </c>
+      <c r="F44" t="n">
+        <v>148</v>
+      </c>
+      <c r="G44" t="n">
+        <v>21060400</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>RF머트리얼즈</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>327260</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
         <v>36750</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F45" t="n">
         <v>1088</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G45" t="n">
         <v>39984000</v>
       </c>
-      <c r="H43" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -908,19 +908,21 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>33750</v>
       </c>
       <c r="F15" t="n">
-        <v>882</v>
+        <v>585</v>
       </c>
       <c r="G15" t="n">
-        <v>29767500</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>19743750</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-5.99</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -940,17 +942,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>33750</v>
       </c>
       <c r="F16" t="n">
-        <v>585</v>
+        <v>882</v>
       </c>
       <c r="G16" t="n">
-        <v>19743750</v>
+        <v>29767500</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,17 +473,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -492,126 +492,126 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>113700</v>
+        <v>1856000</v>
       </c>
       <c r="F2" t="n">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="G2" t="n">
-        <v>9891900</v>
+        <v>35264000</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>78600</v>
+        <v>49000</v>
       </c>
       <c r="F3" t="n">
-        <v>264</v>
+        <v>126</v>
       </c>
       <c r="G3" t="n">
-        <v>20750400</v>
+        <v>6174000</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>114500</v>
+        <v>13340</v>
       </c>
       <c r="F4" t="n">
-        <v>85</v>
+        <v>181</v>
       </c>
       <c r="G4" t="n">
-        <v>9732500</v>
+        <v>2414540</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>24100</v>
+        <v>29800</v>
       </c>
       <c r="F5" t="n">
-        <v>406</v>
+        <v>38</v>
       </c>
       <c r="G5" t="n">
-        <v>9784600</v>
+        <v>1132400</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -620,30 +620,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>33750</v>
+        <v>269500</v>
       </c>
       <c r="F6" t="n">
-        <v>290</v>
+        <v>93</v>
       </c>
       <c r="G6" t="n">
-        <v>9787500</v>
+        <v>25063500</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -652,160 +652,158 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>92500</v>
+        <v>330000</v>
       </c>
       <c r="F7" t="n">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="G7" t="n">
-        <v>7215000</v>
+        <v>7920000</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>25550</v>
+        <v>35550</v>
       </c>
       <c r="F8" t="n">
-        <v>377</v>
+        <v>396</v>
       </c>
       <c r="G8" t="n">
-        <v>9632350</v>
+        <v>14077800</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>25400</v>
+        <v>574000</v>
       </c>
       <c r="F9" t="n">
-        <v>379</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>9626600</v>
+        <v>6314000</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>21800</v>
+        <v>165900</v>
       </c>
       <c r="F10" t="n">
-        <v>581</v>
+        <v>13</v>
       </c>
       <c r="G10" t="n">
-        <v>12665800</v>
+        <v>2156700</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>32250</v>
+        <v>91300</v>
       </c>
       <c r="F11" t="n">
-        <v>579</v>
+        <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>18672750</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-11.16</v>
-      </c>
+        <v>1095600</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -814,64 +812,62 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>27400</v>
+        <v>224500</v>
       </c>
       <c r="F12" t="n">
-        <v>1086</v>
+        <v>63</v>
       </c>
       <c r="G12" t="n">
-        <v>29756400</v>
+        <v>14143500</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105800</v>
+        <v>6010</v>
       </c>
       <c r="F13" t="n">
-        <v>180</v>
+        <v>2344</v>
       </c>
       <c r="G13" t="n">
-        <v>19044000</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-9.109999999999999</v>
-      </c>
+        <v>14087440</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -880,64 +876,62 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>124700</v>
+        <v>25800</v>
       </c>
       <c r="F14" t="n">
-        <v>159</v>
+        <v>19</v>
       </c>
       <c r="G14" t="n">
-        <v>19827300</v>
+        <v>490200</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>33750</v>
+        <v>127000</v>
       </c>
       <c r="F15" t="n">
-        <v>585</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>19743750</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-5.99</v>
-      </c>
+        <v>127000</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -946,30 +940,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>33750</v>
+        <v>49150</v>
       </c>
       <c r="F16" t="n">
-        <v>882</v>
+        <v>287</v>
       </c>
       <c r="G16" t="n">
-        <v>29767500</v>
+        <v>14106050</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -978,64 +972,62 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>86300</v>
+        <v>19280</v>
       </c>
       <c r="F17" t="n">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="G17" t="n">
-        <v>20798300</v>
+        <v>14093680</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>21000</v>
+        <v>19740</v>
       </c>
       <c r="F18" t="n">
-        <v>1005</v>
+        <v>374</v>
       </c>
       <c r="G18" t="n">
-        <v>21105000</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.48</v>
-      </c>
+        <v>7382760</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1044,128 +1036,126 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>131200</v>
+        <v>25150</v>
       </c>
       <c r="F19" t="n">
-        <v>305</v>
+        <v>560</v>
       </c>
       <c r="G19" t="n">
-        <v>40016000</v>
+        <v>14084000</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>21900</v>
+        <v>153500</v>
       </c>
       <c r="F20" t="n">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="G20" t="n">
-        <v>5015100</v>
+        <v>2609500</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>135300</v>
+        <v>32100</v>
       </c>
       <c r="F21" t="n">
-        <v>155</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>20971500</v>
+        <v>128400</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>171200</v>
+        <v>6240</v>
       </c>
       <c r="F22" t="n">
-        <v>231</v>
+        <v>2258</v>
       </c>
       <c r="G22" t="n">
-        <v>39547200</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-1.21</v>
-      </c>
+        <v>14089920</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1174,62 +1164,62 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1674000</v>
+        <v>15520</v>
       </c>
       <c r="F23" t="n">
-        <v>75</v>
+        <v>908</v>
       </c>
       <c r="G23" t="n">
-        <v>125550000</v>
+        <v>14092160</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>50900</v>
+        <v>24200</v>
       </c>
       <c r="F24" t="n">
-        <v>413</v>
+        <v>16</v>
       </c>
       <c r="G24" t="n">
-        <v>21021700</v>
+        <v>387200</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1238,350 +1228,350 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>14970</v>
+        <v>36300</v>
       </c>
       <c r="F25" t="n">
-        <v>1403</v>
+        <v>388</v>
       </c>
       <c r="G25" t="n">
-        <v>21002910</v>
+        <v>14084400</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>28100</v>
+        <v>279500</v>
       </c>
       <c r="F26" t="n">
-        <v>747</v>
+        <v>31</v>
       </c>
       <c r="G26" t="n">
-        <v>20990700</v>
+        <v>8664500</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>260000</v>
+        <v>132600</v>
       </c>
       <c r="F27" t="n">
-        <v>485</v>
+        <v>56</v>
       </c>
       <c r="G27" t="n">
-        <v>126100000</v>
+        <v>7425600</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>311500</v>
+        <v>44600</v>
       </c>
       <c r="F28" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G28" t="n">
-        <v>20870500</v>
+        <v>3166600</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>36300</v>
+        <v>147100</v>
       </c>
       <c r="F29" t="n">
-        <v>579</v>
+        <v>7</v>
       </c>
       <c r="G29" t="n">
-        <v>21017700</v>
+        <v>1029700</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>577000</v>
+        <v>33500</v>
       </c>
       <c r="F30" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="G30" t="n">
-        <v>20772000</v>
+        <v>335000</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>20900</v>
+        <v>143100</v>
       </c>
       <c r="F31" t="n">
-        <v>1005</v>
+        <v>50</v>
       </c>
       <c r="G31" t="n">
-        <v>21004500</v>
+        <v>7155000</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>150100</v>
+        <v>83800</v>
       </c>
       <c r="F32" t="n">
-        <v>140</v>
+        <v>73</v>
       </c>
       <c r="G32" t="n">
-        <v>21014000</v>
+        <v>6117400</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>94200</v>
+        <v>42300</v>
       </c>
       <c r="F33" t="n">
-        <v>297</v>
+        <v>11</v>
       </c>
       <c r="G33" t="n">
-        <v>27977400</v>
+        <v>465300</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>116400</v>
+        <v>81200</v>
       </c>
       <c r="F34" t="n">
-        <v>180</v>
+        <v>91</v>
       </c>
       <c r="G34" t="n">
-        <v>20952000</v>
+        <v>7389200</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>22250</v>
+        <v>113700</v>
       </c>
       <c r="F35" t="n">
-        <v>1348</v>
+        <v>87</v>
       </c>
       <c r="G35" t="n">
-        <v>29993000</v>
+        <v>9891900</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1590,52 +1580,52 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>173300</v>
+        <v>78600</v>
       </c>
       <c r="F36" t="n">
-        <v>231</v>
+        <v>264</v>
       </c>
       <c r="G36" t="n">
-        <v>40032300</v>
+        <v>20750400</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>35900</v>
+        <v>114500</v>
       </c>
       <c r="F37" t="n">
-        <v>585</v>
+        <v>85</v>
       </c>
       <c r="G37" t="n">
-        <v>21001500</v>
+        <v>9732500</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1650,243 +1640,1309 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>21500</v>
+        <v>24100</v>
       </c>
       <c r="F38" t="n">
-        <v>977</v>
+        <v>406</v>
       </c>
       <c r="G38" t="n">
-        <v>21005500</v>
+        <v>9784600</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>307500</v>
+        <v>33750</v>
       </c>
       <c r="F39" t="n">
-        <v>81</v>
+        <v>290</v>
       </c>
       <c r="G39" t="n">
-        <v>24907500</v>
+        <v>9787500</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>129300</v>
+        <v>92500</v>
       </c>
       <c r="F40" t="n">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="G40" t="n">
-        <v>20946600</v>
+        <v>7215000</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>54200</v>
+        <v>25550</v>
       </c>
       <c r="F41" t="n">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="G41" t="n">
-        <v>20975400</v>
+        <v>9632350</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>139000</v>
+        <v>25400</v>
       </c>
       <c r="F42" t="n">
-        <v>151</v>
+        <v>379</v>
       </c>
       <c r="G42" t="n">
-        <v>20989000</v>
+        <v>9626600</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>33800</v>
+        <v>21800</v>
       </c>
       <c r="F43" t="n">
-        <v>621</v>
+        <v>581</v>
       </c>
       <c r="G43" t="n">
-        <v>20989800</v>
+        <v>12665800</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>142300</v>
+        <v>32250</v>
       </c>
       <c r="F44" t="n">
-        <v>148</v>
+        <v>579</v>
       </c>
       <c r="G44" t="n">
-        <v>21060400</v>
-      </c>
-      <c r="H44" t="inlineStr"/>
+        <v>18672750</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-11.16</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>27400</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1086</v>
+      </c>
+      <c r="G45" t="n">
+        <v>29756400</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>한전기술</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>052690</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>105800</v>
+      </c>
+      <c r="F46" t="n">
+        <v>180</v>
+      </c>
+      <c r="G46" t="n">
+        <v>19044000</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-9.109999999999999</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>엘앤에프</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>066970</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>비중 확대</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>124700</v>
+      </c>
+      <c r="F47" t="n">
+        <v>159</v>
+      </c>
+      <c r="G47" t="n">
+        <v>19827300</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>아이티센글로벌</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>124500</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F48" t="n">
+        <v>585</v>
+      </c>
+      <c r="G48" t="n">
+        <v>19743750</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-5.99</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>아이티센글로벌</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>124500</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F49" t="n">
+        <v>882</v>
+      </c>
+      <c r="G49" t="n">
+        <v>29767500</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SK바이오팜</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>326030</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>86300</v>
+      </c>
+      <c r="F50" t="n">
+        <v>241</v>
+      </c>
+      <c r="G50" t="n">
+        <v>20798300</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>010140</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1005</v>
+      </c>
+      <c r="G51" t="n">
+        <v>21105000</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>엘앤에프</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>066970</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>131200</v>
+      </c>
+      <c r="F52" t="n">
+        <v>305</v>
+      </c>
+      <c r="G52" t="n">
+        <v>40016000</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>086450</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>비중 확대</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>21900</v>
+      </c>
+      <c r="F53" t="n">
+        <v>229</v>
+      </c>
+      <c r="G53" t="n">
+        <v>5015100</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SK이노베이션</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>096770</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>135300</v>
+      </c>
+      <c r="F54" t="n">
+        <v>155</v>
+      </c>
+      <c r="G54" t="n">
+        <v>20971500</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>KB금융</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>105560</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>171200</v>
+      </c>
+      <c r="F55" t="n">
+        <v>231</v>
+      </c>
+      <c r="G55" t="n">
+        <v>39547200</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-1.21</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1674000</v>
+      </c>
+      <c r="F56" t="n">
+        <v>75</v>
+      </c>
+      <c r="G56" t="n">
+        <v>125550000</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>현대해상</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>001450</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>50900</v>
+      </c>
+      <c r="F57" t="n">
+        <v>413</v>
+      </c>
+      <c r="G57" t="n">
+        <v>21021700</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>한국화장품제조</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>003350</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>14970</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1403</v>
+      </c>
+      <c r="G58" t="n">
+        <v>21002910</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>대한항공</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>003490</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>28100</v>
+      </c>
+      <c r="F59" t="n">
+        <v>747</v>
+      </c>
+      <c r="G59" t="n">
+        <v>20990700</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>260000</v>
+      </c>
+      <c r="F60" t="n">
+        <v>485</v>
+      </c>
+      <c r="G60" t="n">
+        <v>126100000</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>LS</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>006260</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>311500</v>
+      </c>
+      <c r="F61" t="n">
+        <v>67</v>
+      </c>
+      <c r="G61" t="n">
+        <v>20870500</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>GS건설</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>006360</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>36300</v>
+      </c>
+      <c r="F62" t="n">
+        <v>579</v>
+      </c>
+      <c r="G62" t="n">
+        <v>21017700</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>삼성SDI</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>006400</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>577000</v>
+      </c>
+      <c r="F63" t="n">
+        <v>36</v>
+      </c>
+      <c r="G63" t="n">
+        <v>20772000</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>010140</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>20900</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1005</v>
+      </c>
+      <c r="G64" t="n">
+        <v>21004500</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>S-OIL</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>010950</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>150100</v>
+      </c>
+      <c r="F65" t="n">
+        <v>140</v>
+      </c>
+      <c r="G65" t="n">
+        <v>21014000</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SK텔레콤</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>017670</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>94200</v>
+      </c>
+      <c r="F66" t="n">
+        <v>297</v>
+      </c>
+      <c r="G66" t="n">
+        <v>27977400</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>한전기술</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>052690</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>116400</v>
+      </c>
+      <c r="F67" t="n">
+        <v>180</v>
+      </c>
+      <c r="G67" t="n">
+        <v>20952000</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>086450</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>22250</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1348</v>
+      </c>
+      <c r="G68" t="n">
+        <v>29993000</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>KB금융</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>105560</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>173300</v>
+      </c>
+      <c r="F69" t="n">
+        <v>231</v>
+      </c>
+      <c r="G69" t="n">
+        <v>40032300</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>아이티센글로벌</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>124500</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>35900</v>
+      </c>
+      <c r="F70" t="n">
+        <v>585</v>
+      </c>
+      <c r="G70" t="n">
+        <v>21001500</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>아스플로</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>159010</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>21500</v>
+      </c>
+      <c r="F71" t="n">
+        <v>977</v>
+      </c>
+      <c r="G71" t="n">
+        <v>21005500</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>196170</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>307500</v>
+      </c>
+      <c r="F72" t="n">
+        <v>81</v>
+      </c>
+      <c r="G72" t="n">
+        <v>24907500</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>222800</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>129300</v>
+      </c>
+      <c r="F73" t="n">
+        <v>162</v>
+      </c>
+      <c r="G73" t="n">
+        <v>20946600</v>
+      </c>
+      <c r="H73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>54200</v>
+      </c>
+      <c r="F74" t="n">
+        <v>387</v>
+      </c>
+      <c r="G74" t="n">
+        <v>20975400</v>
+      </c>
+      <c r="H74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>세아제강</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>306200</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>139000</v>
+      </c>
+      <c r="F75" t="n">
+        <v>151</v>
+      </c>
+      <c r="G75" t="n">
+        <v>20989000</v>
+      </c>
+      <c r="H75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>33800</v>
+      </c>
+      <c r="F76" t="n">
+        <v>621</v>
+      </c>
+      <c r="G76" t="n">
+        <v>20989800</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>HD현대에너지솔루션</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>322000</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>142300</v>
+      </c>
+      <c r="F77" t="n">
+        <v>148</v>
+      </c>
+      <c r="G77" t="n">
+        <v>21060400</v>
+      </c>
+      <c r="H77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
         <is>
           <t>RF머트리얼즈</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>327260</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
         <v>36750</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F78" t="n">
         <v>1088</v>
       </c>
-      <c r="G45" t="n">
+      <c r="G78" t="n">
         <v>39984000</v>
       </c>
-      <c r="H45" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
